--- a/excel_config/indir/怪物.xlsx
+++ b/excel_config/indir/怪物.xlsx
@@ -830,12 +830,12 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string[][]</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>int[]</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
@@ -934,12 +934,12 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>[["item","items_LingCao","1","3","5"],["item","items_HuiQiDan","1","1","2"]]</t>
+          <t>item:items_LingCao:1:3:5|item:items_HuiQiDan:1:1:2</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>[1]</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" s="8" t="n">
@@ -1000,12 +1000,12 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>[["item","items_LingCao","1","3","5"],["item","items_HuiQiDan","1","1","2"]]</t>
+          <t>item:items_LingCao:1:3:5|item:items_HuiQiDan:1:1:2</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>[1]</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" s="8" t="n">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>[["item","items_LingCao","1","3","5"],["item","items_HuiQiDan","1","1","2"]]</t>
+          <t>item:items_LingCao:1:3:5|item:items_HuiQiDan:1:1:2</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>[1]</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" s="8" t="n">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>[["item","items_LingCao","1","3","5"],["item","items_HuiQiDan","1","1","2"]]</t>
+          <t>item:items_LingCao:1:3:5|item:items_HuiQiDan:1:1:2</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>[1]</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" s="8" t="n">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>[["item","items_LingCao","1","3","5"],["item","items_HuiQiDan","1","1","2"]]</t>
+          <t>item:items_LingCao:1:3:5|item:items_HuiQiDan:1:1:2</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>[1]</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" s="8" t="n">
@@ -1264,12 +1264,12 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>[["item","items_LingCao","1","3","5"],["item","items_HuiQiDan","1","1","2"]]</t>
+          <t>item:items_LingCao:1:3:5|item:items_HuiQiDan:1:1:2</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>[1]</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" s="8" t="n">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>[["item","items_LingCao","1","3","5"],["item","items_HuiQiDan","1","1","2"]]</t>
+          <t>item:items_LingCao:1:3:5|item:items_HuiQiDan:1:1:2</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>[1]</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I11" s="8" t="n">
@@ -1396,12 +1396,12 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>[["item","items_LingCao","1","3","5"],["item","items_HuiQiDan","1","1","2"]]</t>
+          <t>item:items_LingCao:1:3:5|item:items_HuiQiDan:1:1:2</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>[1]</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" s="8" t="n">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>[["item","items_LingCao","1","3","5"],["item","items_HuiQiDan","1","1","2"]]</t>
+          <t>item:items_LingCao:1:3:5|item:items_HuiQiDan:1:1:2</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>[1]</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" s="8" t="n">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>[["item","items_LingCao","1","3","5"],["item","items_HuiQiDan","1","1","2"]]</t>
+          <t>item:items_LingCao:1:3:5|item:items_HuiQiDan:1:1:2</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>[1,2]</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I14" s="10" t="n">
